--- a/watchlist_consolidado.xlsx
+++ b/watchlist_consolidado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="watchlist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="watchlist" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'watchlist'!$A$1:$D$287</definedName>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D287"/>
+  <dimension ref="A1:D307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -524,17 +524,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>https://ada.com/careers/</t>
+          <t>https://job-boards.greenhouse.io/adahealth</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>[Salud] Comprobador de síntomas con IA</t>
+          <t>[Salud] Comprobador de síntomas con IA [ATS auto-descubierto 22-09-2026 via API publica; slug=adahealth]</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://www.adyen.com/careers</t>
+          <t>https://job-boards.greenhouse.io/adyen</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>[Fintech]</t>
+          <t>[Fintech] [ATS auto-descubierto 22-09-2026 via API publica; slug=adyen]</t>
         </is>
       </c>
     </row>
@@ -610,15 +610,19 @@
           <t>Air Apps</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/airapps</t>
+        </is>
+      </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Remote (pero rol onsite en Lisboa) · España / Lisboa · no tenías un enlace válido guardado para esta empresa en tu tracker</t>
+          <t>Remote (pero rol onsite en Lisboa) · España / Lisboa · no tenías un enlace válido guardado para esta empresa en tu tracker [ATS auto-descubierto 22-09-2026 via API publica; slug=airapps] [22-09-2026: OJO - las vacantes de Product Designer en Ashby listan muchas ciudades (incl. Madrid, Barcelona) pero la descripcion real dice "fully onsite position, based at our office in Lisbon". Las etiquetas de ciudad son enganosas: verificar el cuerpo de la oferta, no solo la ubicacion, antes de puntuar.]</t>
         </is>
       </c>
     </row>
@@ -635,12 +639,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Barcelona &amp; CO · Workable</t>
+          <t>Híbrido · Barcelona &amp; CO · Workable [ATS detectado 22-09-2026 (workable, slug=airhelp) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -652,17 +656,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>https://airtable.com/careers</t>
+          <t>https://job-boards.greenhouse.io/airtable</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS auto-descubierto 22-09-2026 via API publica; slug=airtable]</t>
         </is>
       </c>
     </row>
@@ -701,12 +705,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Madrid · Aparece junto a INNOCV Solutions en tu tracker, revisar relación entre ambas</t>
+          <t>Híbrido · Madrid · Aparece junto a INNOCV Solutions en tu tracker, revisar relación entre ambas [ATS detectado 22-09-2026 (teamtailor, slug=www) pero check_boards.py aun no lo soporta - revisar a mano] [22-09-2026: jobs.innocv.com devuelve una vacante de UX/UI Designer, pero ese mismo dominio tambien aparece para la empresa INNOCV Solutions -&gt; podria ser un portal de agencia/staffing que lista clientes, no el board propio de Alkemy Iberia. Verificar a mano quien es el empleador real antes de puntuar.] [22-09-2026 CORREGIDO: confirmado por la propia usuaria que Alkemy es real (ha tenido entrevistas alli); la oferta en jobs.innocv.com nombra explicitamente al empleador ("We are part of the Alkemy Group") -&gt; INNOCV es solo la plataforma de reclutamiento que usa Alkemy, no una agencia que oculta al cliente. Se puntua con normalidad, con el -8 de consultoria que ya marca la regla.]</t>
         </is>
       </c>
     </row>
@@ -806,17 +810,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>https://amplitude.com/careers</t>
+          <t>https://job-boards.greenhouse.io/amplitude</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS auto-descubierto 22-09-2026 via API publica; slug=amplitude]</t>
         </is>
       </c>
     </row>
@@ -890,17 +894,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>https://asana.com/jobs</t>
+          <t>https://job-boards.greenhouse.io/asana</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS auto-descubierto 22-09-2026 via API publica; slug=asana]</t>
         </is>
       </c>
     </row>
@@ -912,17 +916,17 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>https://www.ashoka.org/en/jobs</t>
+          <t>https://jobs.lever.co/ashoka</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>[Impacto social] Red global de emprendimiento social</t>
+          <t>[Impacto social] Red global de emprendimiento social [ATS auto-descubierto 22-09-2026 via API publica; slug=ashoka]</t>
         </is>
       </c>
     </row>
@@ -978,17 +982,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>https://automattic.com/work-with-us/</t>
+          <t>https://job-boards.greenhouse.io/automatticcareers</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>[Remote-first] Cultura 100% remota (WordPress.com)</t>
+          <t>[Remote-first] Cultura 100% remota (WordPress.com) [22-09-2026: ATS greenhouse confirmado (slug automatticcareers); hoy sin vacantes de diseno (16 vacantes abiertas, ninguna de design). No cuenta hoy.]</t>
         </is>
       </c>
     </row>
@@ -1000,17 +1004,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>https://www.babbel.com/careers</t>
+          <t>https://jobs.ashbyhq.com/babbel</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>[EdTech]</t>
+          <t>[EdTech] [ATS auto-descubierto 22-09-2026 via API publica; slug=babbel]</t>
         </is>
       </c>
     </row>
@@ -1022,17 +1026,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>https://www.backmarket.com/en-us/careers</t>
+          <t>https://jobs.ashbyhq.com/backmarket</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] Marketplace de tecnología reacondicionada</t>
+          <t>[Ecología] Marketplace de tecnología reacondicionada [ATS auto-descubierto 22-09-2026 via API publica; slug=backmarket]</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1119,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>[Spain/Madrid] Sede en Madrid, equipo de diseño digital grande</t>
+          <t>[Spain/Madrid] Sede en Madrid, equipo de diseño digital grande [ATS detectado 22-09-2026 (workday, slug=bbva) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -1132,17 +1136,17 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>https://www.benjerry.com/whats-new/careers</t>
+          <t>https://jobs.ashbyhq.com/ben</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>[Valores/B-Corp] Identidad activista fuerte, propiedad de Unilever</t>
+          <t>[Valores/B-Corp] Identidad activista fuerte, propiedad de Unilever [ATS auto-descubierto 22-09-2026 via API publica; slug=ben]</t>
         </is>
       </c>
     </row>
@@ -1154,17 +1158,17 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.bendingspoons.com/positions/69970a2579dbe4d52a84544a?utm_medium=job_post&amp;utm_source=linkedin&amp;utm_campaign=69e6bf0b863053fddef78053</t>
+          <t>https://jobs.bendingspoons.com/</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Remote · Milan / London / Madrid / Warsaw · Matriz de WeTransfer, Meetup, Evernote y otras adquisiciones — verás su careers en un único portal</t>
+          <t>Remote · Milan / London / Madrid / Warsaw · Matriz de WeTransfer, Meetup, Evernote y otras adquisiciones — verás su careers en un único portal [22-09-2026: UX/UI designer confirmado abierto, Madrid u oficinas EU o remoto desde pais elegible, salario publicado 66-108k EUR. Aplicar ya.]</t>
         </is>
       </c>
     </row>
@@ -1176,17 +1180,17 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>https://benevity.com/careers</t>
+          <t>https://jobs.ashbyhq.com/benevity</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>[Impacto social] Software de donaciones corporativas</t>
+          <t>[Impacto social] Software de donaciones corporativas [ATS auto-descubierto 22-09-2026 via API publica; slug=benevity]</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1202,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>https://www.betterup.com/careers</t>
+          <t>https://jobs.ashbyhq.com/betterup</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>[Salud] Coaching y bienestar laboral</t>
+          <t>[Salud] Coaching y bienestar laboral [ATS auto-descubierto 22-09-2026 via API publica; slug=betterup]</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1242,17 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://www.beyondmeat.com/careers/</t>
+          <t>https://job-boards.greenhouse.io/beyond</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] Proteína vegetal</t>
+          <t>[Ecología] Proteína vegetal [ATS auto-descubierto 22-09-2026 via API publica; slug=beyond]</t>
         </is>
       </c>
     </row>
@@ -1260,17 +1264,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://www.bighealth.com/careers/</t>
+          <t>https://jobs.lever.co/bighealth</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>[Salud] Terapia digital para sueño y ansiedad</t>
+          <t>[Salud] Terapia digital para sueño y ansiedad [ATS auto-descubierto 22-09-2026 via API publica; slug=bighealth]</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1286,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>https://www.bitfinex.com/</t>
+          <t>https://careers.bitfinex.com</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>recruitee</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Remote Worldwide · CET Timezone</t>
+          <t>Remote Worldwide · CET Timezone [22-09-2026: ATS auto-descubierto (recruitee) via discover_v2 sistematizado, sin oferta de diseno hoy salvo excepcion anotada aparte.]</t>
         </is>
       </c>
     </row>
@@ -1304,17 +1308,17 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/search-results/?currentJobId=4425786526&amp;eBP=BUDGET_EXHAUSTED_JOB&amp;refId=v0kCFj2s0os9G8OJiO%2Byqg%3D%3D&amp;trackingId=0DwVVxnE0c%2Fa1pukVF4gtg%3D%3D&amp;keywords=product+designer&amp;origin=JOB_SEARCH_PAGE_JOB_FILTER&amp;referralSearchId=3UXZO4Zvpbd%2BLxvWL%2Fmk1Q%3D%3D</t>
+          <t>https://job-boards.greenhouse.io/bitpanda</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Barcelona · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Híbrido · Barcelona · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=bitpanda]</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1401,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>icims</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>[Travel]</t>
+          <t>[Travel] [ATS detectado 22-09-2026 (icims, slug=internal-workingatbooking) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -1436,17 +1440,17 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>https://cabify.com/en/careers</t>
+          <t>https://job-boards.greenhouse.io/cabify</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>[Spain/Madrid] Sede en Madrid</t>
+          <t>[Spain/Madrid] Sede en Madrid [ATS auto-descubierto 22-09-2026 via API publica; slug=cabify]</t>
         </is>
       </c>
     </row>
@@ -1458,17 +1462,17 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>https://www.calm.com/careers</t>
+          <t>https://job-boards.greenhouse.io/calm</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>[Salud] Meditación y salud mental</t>
+          <t>[Salud] Meditación y salud mental [ATS auto-descubierto 22-09-2026 via API publica; slug=calm]</t>
         </is>
       </c>
     </row>
@@ -1480,17 +1484,17 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>https://canonical.com/careers</t>
+          <t>https://job-boards.greenhouse.io/canonical</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Remote · EMEA</t>
+          <t>Remote · EMEA [ATS auto-descubierto 22-09-2026 via API publica; slug=canonical]</t>
         </is>
       </c>
     </row>
@@ -1568,17 +1572,17 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>https://www.charitywater.org/careers</t>
+          <t>https://jobs.lever.co/charitywater</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>[Impacto social] ONG de acceso a agua potable</t>
+          <t>[Impacto social] ONG de acceso a agua potable [ATS auto-descubierto 22-09-2026 via API publica; slug=charitywater]</t>
         </is>
       </c>
     </row>
@@ -1656,17 +1660,17 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/search-results/?currentJobId=4437413195&amp;eBP=CwEAAAGfPO18uo1iDMX9yh2bLBGLho_eQRfgohPvU4iQ6mzLj3JWykSVFWbaw1JrowUB_zWSfz1sCA9Uf9QRo-dvhrMSbx6gVgo_3hVdw3PH6pvDIoe0DLvicFL9EYqoCmoEyTOj9acIYZK0rt5eQvgI010JgY-jqfqcU0s9EptN8jP434y4weihcbOGs0WsQg2KJXJRKcYjL1p1q8BVWShi6enT2ShWUEIGOFhPUj86TrHb6pf7nO3xh-U3N5ZRomcolHxtEhLZ3CwXqDVija6JFRDXR2DGfBUfCaHuMmMVS3P3IW0Uiwn3Jc8SES3H1O7IFcsStslop62vGifX-KRsS6sD_clgd8PqweW56XKoSrvP4_xVpHyXUKVbquiQWpW8NZ2CxASTqUWYvAFUJMBZDWM8cwNmJCY9ghSq1sUpTvJR4i4HJJx56lBvM6ene8C-HtcPSOYtbFOr7zyBXHpHK6EJoChvXZxumyc&amp;refId=c0ofM11mwxooRCDDUCb2rQ%3D%3D&amp;trackingId=c7sFFQVZhzBBLlXfP65r7Q%3D%3D&amp;keywords=product%20Designer%20posted%20in%20the%20past%2024%20hours&amp;origin=SEMANTIC_SEARCH_HISTORY&amp;geoId=105646813&amp;distance=25</t>
+          <t>https://jobs.lever.co/codeway</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Hybrid · Full-time · Barcelona · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Hybrid · Full-time · Barcelona · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=codeway]</t>
         </is>
       </c>
     </row>
@@ -1678,17 +1682,17 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/careers</t>
+          <t>https://jobs.ashbyhq.com/coinbase</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>[Fintech] Confirmado por Greenhouse como cliente</t>
+          <t>[Fintech] Confirmado por Greenhouse como cliente [ATS auto-descubierto 22-09-2026 via API publica; slug=coinbase]</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1704,17 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>https://www.contentful.com/careers/</t>
+          <t>https://job-boards.greenhouse.io/contentful</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS auto-descubierto 22-09-2026 via API publica; slug=contentful]</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1748,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>https://careers.coursera.com/</t>
+          <t>https://job-boards.greenhouse.io/coursera</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>[EdTech]</t>
+          <t>[EdTech] [ATS auto-descubierto 22-09-2026 via API publica; slug=coursera]</t>
         </is>
       </c>
     </row>
@@ -1854,17 +1858,17 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.deel.com/deel/job-details/0380d24a-cc3e-4001-8da0-62dcbbece6cd/overview?source=linkedin</t>
+          <t>https://jobs.ashbyhq.com/Deel</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>EMEA / US / LATAM · Remote</t>
+          <t>EMEA / US / LATAM · Remote [ATS auto-descubierto 22-09-2026 via API publica; slug=Deel]</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1934,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>[Accesibilidad] Empresa dedicada 100% a accesibilidad, encaje directo con tu especialización</t>
+          <t>[Accesibilidad] Empresa dedicada 100% a accesibilidad, encaje directo con tu especialización [22-09-2026: empresa de accesibilidad (encaja mucho con el perfil), pero hoy sin Product/UX Designer abierto (solo roles US remote no-diseno + 1 en India). Vigilar.]</t>
         </is>
       </c>
     </row>
@@ -1942,17 +1946,17 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4397475756/?trk=eml-email_job_alert_digest_01-primary_job_list-0-jobcard_body_0_jobid_4397475756_ssid_5198310161_fmid_dnyviv~mopgipw9~5p&amp;refId=wcevKSO3cicv%2BDm8d%2BsKog%3D%3D&amp;trackingId=ooNXlO2X2HBYkWb3jmqE%2Fg%3D%3D</t>
+          <t>https://jobs.ashbyhq.com/docplanner</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Remoto · España · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remoto · España · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=docplanner]</t>
         </is>
       </c>
     </row>
@@ -1964,17 +1968,17 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>https://www.doctolib.com/careers</t>
+          <t>https://job-boards.greenhouse.io/doctolib</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>[Salud] Plataforma de citas médicas, líder en Europa</t>
+          <t>[Salud] Plataforma de citas médicas, líder en Europa [ATS auto-descubierto 22-09-2026 via API publica; slug=doctolib]</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1995,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>icims</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS detectado 22-09-2026 (icims, slug=www) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -2026,17 +2030,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/</t>
+          <t>https://job-boards.greenhouse.io/dropbox</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS auto-descubierto 22-09-2026 via API publica; slug=dropbox]</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2079,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>breezyhr</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>[EdTech] Confirmado por Greenhouse como cliente</t>
+          <t>[EdTech] Confirmado por Greenhouse como cliente [ATS detectado 22-09-2026 (breezyhr, slug=duolingo) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2128,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] Buscador que planta árboles con los beneficios</t>
+          <t>[Ecología] Buscador que planta árboles con los beneficios [22-09-2026: deteccion de Workable devolvio un slug invalido ("oops"), descartar, revisar a mano.]</t>
         </is>
       </c>
     </row>
@@ -2180,17 +2184,17 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4368681647/</t>
+          <t>https://job-boards.greenhouse.io/elastic</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Remoto · España · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remoto · España · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=elastic]</t>
         </is>
       </c>
     </row>
@@ -2264,17 +2268,17 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>https://www.epicgames.com/site/en-US/careers</t>
+          <t>https://job-boards.greenhouse.io/epicgames</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>[Gaming]</t>
+          <t>[Gaming] [ATS auto-descubierto 22-09-2026 via API publica; slug=epicgames]</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2388,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>[Spain/Madrid] Sede en Barcelona · También visto en tu tracker de aplicaciones: Presencial / híbrido · Madrid / Barcelona</t>
+          <t>[Spain/Madrid] Sede en Barcelona · También visto en tu tracker de aplicaciones: Presencial / híbrido · Madrid / Barcelona [22-09-2026: oferta de Senior Product Designer ya cerrada. No cuenta hoy, vigilar.]</t>
         </is>
       </c>
     </row>
@@ -2440,17 +2444,17 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>https://www.figma.com/careers/</t>
+          <t>https://job-boards.greenhouse.io/figma</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B] Herramienta que ya usas, buen fit cultural · También visto en tu tracker de aplicaciones: Remote (solo US) / hubs US · Madrid / US</t>
+          <t>[SaaS B2B] Herramienta que ya usas, buen fit cultural · También visto en tu tracker de aplicaciones: Remote (solo US) / hubs US · Madrid / US [ATS auto-descubierto 22-09-2026 via API publica; slug=figma]</t>
         </is>
       </c>
     </row>
@@ -2482,15 +2486,19 @@
           <t>FitXR</t>
         </is>
       </c>
-      <c r="B94" s="4" t="n"/>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/fitxr</t>
+        </is>
+      </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Fully Remote · España / UK / US · no tenías un enlace válido guardado para esta empresa en tu tracker</t>
+          <t>Fully Remote · España / UK / US · no tenías un enlace válido guardado para esta empresa en tu tracker [ATS auto-descubierto 22-09-2026 via API publica; slug=fitxr]</t>
         </is>
       </c>
     </row>
@@ -2524,17 +2532,17 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>https://team.freshlycosmetics.com/jobs/7655502-ux-ui-designer</t>
+          <t>https://team.freshlycosmetics.com/jobs</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Reus (Barcelona)</t>
+          <t>Híbrido · Reus (Barcelona) [22-09-2026: ATS auto-descubierto (teamtailor) via discover_v2 sistematizado, sin oferta de diseno hoy salvo excepcion anotada aparte.]</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2564,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Barcelona · enlace guardado es de LinkedIn, no la web oficial · Agencia de diseño global (frog design)</t>
+          <t>Híbrido · Barcelona · enlace guardado es de LinkedIn, no la web oficial · Agencia de diseño global (frog design) [22-09-2026: el descubrimiento automatico devolvio un board de Greenhouse a nombre de "capgeminideutschlandgmbh" -- probable falso positivo (Frog es una consultora de diseno que Capgemini adquirio, puede que comparta ATS, pero no esta confirmado). NO USAR sin verificar a mano.]</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2576,17 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/collections/recommended/?currentJobId=4384232830</t>
+          <t>https://job-boards.greenhouse.io/fundraiseup</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Remoto · España · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remoto · España · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=fundraiseup]</t>
         </is>
       </c>
     </row>
@@ -2612,17 +2620,17 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4228264026/?trk=eml-email_application_confirmation_with_nba_01-applied_jobs-0-jobcard_body&amp;refId=nE6ncSepSiyId8ni3Ms1mQ%3D%3D&amp;trackingId=quUi288KSJCGPZuwccZH8Q%3D%3D</t>
+          <t>https://job-boards.greenhouse.io/general</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Remoto · Madrid · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remoto · Madrid · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=general]</t>
         </is>
       </c>
     </row>
@@ -2656,17 +2664,17 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>https://careers.getyourguide.com/</t>
+          <t>https://job-boards.greenhouse.io/getyourguide</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>[Travel]</t>
+          <t>[Travel] [ATS auto-descubierto 22-09-2026 via API publica; slug=getyourguide]</t>
         </is>
       </c>
     </row>
@@ -2678,17 +2686,17 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/</t>
+          <t>https://job-boards.greenhouse.io/gitlab</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>[Remote-first] Cultura 100% remota, muy documentada</t>
+          <t>[Remote-first] Cultura 100% remota, muy documentada [ATS auto-descubierto 22-09-2026 via API publica; slug=gitlab]</t>
         </is>
       </c>
     </row>
@@ -2700,17 +2708,17 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/collections/recommended/?currentJobId=4408645913&amp;discover=recommended&amp;discoveryOrigin=JOBS_HOME_JYMBII</t>
+          <t>https://jobs.ashbyhq.com/glinttglobal</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Remoto · Spain (cliente Telco) · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remoto · Spain (cliente Telco) · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=glinttglobal]</t>
         </is>
       </c>
     </row>
@@ -2766,17 +2774,17 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>https://www.gofundme.com/c/careers</t>
+          <t>https://job-boards.greenhouse.io/gofundme</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>[Impacto social] Crowdfunding solidario</t>
+          <t>[Impacto social] Crowdfunding solidario [ATS auto-descubierto 22-09-2026 via API publica; slug=gofundme]</t>
         </is>
       </c>
     </row>
@@ -2810,17 +2818,17 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>https://www.gostudent.org/en/careers</t>
+          <t>https://job-boards.greenhouse.io/gostudent</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>[EdTech]</t>
+          <t>[EdTech] [ATS auto-descubierto 22-09-2026 via API publica; slug=gostudent]</t>
         </is>
       </c>
     </row>
@@ -2854,17 +2862,17 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>https://grover.com/careers</t>
+          <t>https://job-boards.greenhouse.io/grover</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] Alquiler de tecnología, economía circular</t>
+          <t>[Ecología] Alquiler de tecnología, economía circular [ATS auto-descubierto 22-09-2026 via API publica; slug=grover]</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2906,17 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>https://www.headspace.com/careers</t>
+          <t>https://job-boards.greenhouse.io/hs</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>[Salud] Meditación y salud mental</t>
+          <t>[Salud] Meditación y salud mental [ATS auto-descubierto 22-09-2026 via API publica; slug=hs]</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3021,12 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] Confirmado: portal en Workable · Energía verde, sede Barcelona, primera eléctrica europea con certificación B-Corp</t>
+          <t>[Ecología] Confirmado: portal en Workable · Energía verde, sede Barcelona, primera eléctrica europea con certificación B-Corp [ATS detectado 22-09-2026 (workable, slug=holaluz) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -3057,12 +3065,12 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Remoto · España / global · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remoto · España / global · enlace guardado es de LinkedIn, no la web oficial [ATS detectado 22-09-2026 (workable, slug=hospitable) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -3074,17 +3082,17 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/search/?alertAction=viewjobs&amp;currentJobId=4410987223&amp;distance=25&amp;f_TPR=a1777973913-&amp;f_WT=1%2C3%2C2&amp;geoId=105646813&amp;keywords=User%20Experience%20Designer&amp;origin=JOB_ALERT_IN_APP_NOTIFICATION&amp;originToLandingJobPostings=4410588797%2C4409338331%2C4389885900%2C4409353134%2C4410560005%2C4410704271&amp;savedSearchId=5198310169&amp;sortBy=R</t>
+          <t>https://jobs.ashbyhq.com/hostinger</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Remote · España / Europa · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remote · España / Europa · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=hostinger]</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3104,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>https://www.hubspot.com/careers</t>
+          <t>https://job-boards.greenhouse.io/hubspot</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -3106,7 +3114,7 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B] Confirmado por Greenhouse como cliente</t>
+          <t>[SaaS B2B] Confirmado por Greenhouse como cliente [ATS auto-descubierto 22-09-2026 via API publica; slug=hubspot]</t>
         </is>
       </c>
     </row>
@@ -3206,17 +3214,17 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/en/about/careers</t>
+          <t>https://careers.idealista.com/jobs</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>[Spain/Madrid] Sede en Madrid</t>
+          <t>[Spain/Madrid] Sede en Madrid [22-09-2026: confirmado ATS teamtailor (careers.idealista.com/jobs.json); hoy solo tiene abierto Creative Designer (marketing/frances), sin Product Designer/UX. No cuenta hoy.]</t>
         </is>
       </c>
     </row>
@@ -3250,17 +3258,17 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>https://impossiblefoods.com/careers</t>
+          <t>https://jobs.ashbyhq.com/impossible-foods</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] Proteína vegetal</t>
+          <t>[Ecología] Proteína vegetal [ATS auto-descubierto 22-09-2026 via API publica; slug=impossible-foods]</t>
         </is>
       </c>
     </row>
@@ -3387,12 +3395,12 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>verificar</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Madrid · Aparece junto a Alkemy Iberia en tu tracker, revisar relación entre ambas</t>
+          <t>Híbrido · Madrid · Aparece junto a Alkemy Iberia en tu tracker, revisar relación entre ambas [ATS detectado 22-09-2026 (teamtailor, slug=www) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3412,17 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>https://www.intercom.com/careers</t>
+          <t>https://job-boards.greenhouse.io/intercom</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS auto-descubierto 22-09-2026 via API publica; slug=intercom]</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3454,19 @@
           <t>IRiS Grupo Tecnológico (Velorum)</t>
         </is>
       </c>
-      <c r="B138" s="4" t="n"/>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/iris</t>
+        </is>
+      </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Remote · Barcelona · no tenías un enlace válido guardado para esta empresa en tu tracker</t>
+          <t>Remote · Barcelona · no tenías un enlace válido guardado para esta empresa en tu tracker [ATS auto-descubierto 22-09-2026 via API publica; slug=iris]</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3478,17 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4390006428/</t>
+          <t>https://job-boards.greenhouse.io/jetbrains</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Hybrid · Madrid · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Hybrid · Madrid · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=jetbrains]</t>
         </is>
       </c>
     </row>
@@ -3488,17 +3500,17 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>https://www.jobandtalent.com/careers</t>
+          <t>https://jobs.lever.co/jobandtalent</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>[Spain/Madrid] Sede en Madrid</t>
+          <t>[Spain/Madrid] Sede en Madrid [ATS auto-descubierto 22-09-2026 via API publica; slug=jobandtalent]</t>
         </is>
       </c>
     </row>
@@ -3510,17 +3522,17 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/collections/recommended/?currentJobId=4405977391&amp;discover=recommended&amp;discoveryOrigin=JOBS_HOME_JYMBII</t>
+          <t>https://jobs.lever.co/jobgether</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>agencia_excluir</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>enlace guardado es de LinkedIn, no la web oficial · Plataforma de empleo remoto, no empresa final — el cliente real no queda identificado en tu tracker</t>
+          <t>enlace guardado es de LinkedIn, no la web oficial · Plataforma de empleo remoto, no empresa final — el cliente real no queda identificado en tu tracker [ATS auto-descubierto 22-09-2026 via API publica; slug=jobgether] [22-09-2026: verificado que Jobgether es una agencia de matching/reclutamiento ("This position is listed on behalf of a partner company"), no el empleador real. No cuenta como oferta oficial. Excluida de check_boards.py.]</t>
         </is>
       </c>
     </row>
@@ -3537,12 +3549,12 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>[Valores/B-Corp] Empresa propiedad de sus empleados (UK)</t>
+          <t>[Valores/B-Corp] Empresa propiedad de sus empleados (UK) [ATS detectado 22-09-2026 (workday, slug=jlp) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -3686,17 +3698,17 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>https://www.khanacademy.org/careers</t>
+          <t>https://job-boards.greenhouse.io/khanacademy</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>[Impacto social/EdTech] Educación gratuita global, sin ánimo de lucro</t>
+          <t>[Impacto social/EdTech] Educación gratuita global, sin ánimo de lucro [ATS auto-descubierto 22-09-2026 via API publica; slug=khanacademy]</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3830,17 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>https://es.indeed.com/jobs?q=product+designer&amp;from=searchOnHP&amp;start=10&amp;vjk=b6be1af10effc5dc</t>
+          <t>https://careers.lansweeper.com</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>recruitee</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Remote-first · Alicante / España · enlace de Indeed, no la web oficial</t>
+          <t>Remote-first · Alicante / España · enlace de Indeed, no la web oficial [22-09-2026: ATS auto-descubierto (recruitee) via discover_v2 sistematizado, sin oferta de diseno hoy salvo excepcion anotada aparte.]</t>
         </is>
       </c>
     </row>
@@ -3840,17 +3852,17 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>https://www.levelaccess.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/level</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>[Accesibilidad] Consultora de accesibilidad, encaje directo con tu especialización</t>
+          <t>[Accesibilidad] Consultora de accesibilidad, encaje directo con tu especialización [ATS auto-descubierto 22-09-2026 via API publica; slug=level]</t>
         </is>
       </c>
     </row>
@@ -3973,12 +3985,12 @@
       <c r="B162" s="4" t="n"/>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>verificar</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Remote · Londres /  / Valencia</t>
+          <t>Remote · Londres /  / Valencia [22-09-2026: mercuryo.io — detectado BambooHR, sin API publica sencilla, revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -4034,17 +4046,17 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>https://miro.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/miro</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B] Producto muy visual, buen fit para product design</t>
+          <t>[SaaS B2B] Producto muy visual, buen fit para product design [ATS auto-descubierto 22-09-2026 via API publica; slug=miro]</t>
         </is>
       </c>
     </row>
@@ -4100,17 +4112,17 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>https://monday.com/careers</t>
+          <t>https://jobs.ashbyhq.com/monday.com</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS auto-descubierto 22-09-2026 via API publica; slug=monday.com]</t>
         </is>
       </c>
     </row>
@@ -4144,17 +4156,17 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>https://www.multiverse.io/en-gb/careers</t>
+          <t>https://jobs.ashbyhq.com/multiverse</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>[EdTech]</t>
+          <t>[EdTech] [ATS auto-descubierto 22-09-2026 via API publica; slug=multiverse]</t>
         </is>
       </c>
     </row>
@@ -4166,17 +4178,17 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/search/?alertAction=viewjobs&amp;currentJobId=4409300083&amp;distance=25&amp;f_TPR=a1777883507-&amp;f_WT=1%2C3%2C2&amp;geoId=105646813&amp;keywords=User%20Experience%20Designer&amp;origin=JOB_ALERT_IN_APP_NOTIFICATION&amp;originToLandingJobPostings=4410075873%2C4408180078%2C4409300083%2C4410061712%2C4398377088%2C4408681111&amp;savedSearchId=5198310169&amp;sortBy=R</t>
+          <t>https://job-boards.greenhouse.io/nix</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Remote · Madrid · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remote · Madrid · enlace guardado es de LinkedIn, no la web oficial [22-09-2026: ATS auto-descubierto (greenhouse) via discover_v2 sistematizado, sin oferta de diseno hoy salvo excepcion anotada aparte.]</t>
         </is>
       </c>
     </row>
@@ -4188,17 +4200,17 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>https://n26.com/en/careers</t>
+          <t>https://job-boards.greenhouse.io/n26</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>[Fintech]</t>
+          <t>[Fintech] [ATS auto-descubierto 22-09-2026 via API publica; slug=n26]</t>
         </is>
       </c>
     </row>
@@ -4320,17 +4332,17 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>https://careers.nintendo.com/jobs/</t>
+          <t>https://job-boards.greenhouse.io/nintendo</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>[Gaming] Confirmado: portal propio, no API pública</t>
+          <t>[Gaming] Confirmado: portal propio, no API pública [ATS auto-descubierto 22-09-2026 via API publica; slug=nintendo]</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4354,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>https://www.notion.so/careers</t>
+          <t>https://jobs.ashbyhq.com/notion</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -4352,7 +4364,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B] Confirmado por Ashby como cliente</t>
+          <t>[SaaS B2B] Confirmado por Ashby como cliente [ATS auto-descubierto 22-09-2026 via API publica; slug=notion]</t>
         </is>
       </c>
     </row>
@@ -4386,17 +4398,17 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>https://oatly.com/careers</t>
+          <t>https://careers.oatly.com/jobs</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] Leche de avena, marca muy activista</t>
+          <t>[Ecología] Leche de avena, marca muy activista [22-09-2026: ATS auto-descubierto (teamtailor) via discover_v2 sistematizado, sin oferta de diseno hoy salvo excepcion anotada aparte.]</t>
         </is>
       </c>
     </row>
@@ -4408,17 +4420,17 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/collections/recommended/?currentJobId=4410299234&amp;discover=recommended&amp;discoveryOrigin=JOBS_HOME_JYMBII&amp;start=24</t>
+          <t>https://job-boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Madrid · enlace guardado es de LinkedIn, no la web oficial · Incluye Auth0 (adquirida por Okta)</t>
+          <t>Híbrido · Madrid · enlace guardado es de LinkedIn, no la web oficial · Incluye Auth0 (adquirida por Okta) [ATS auto-descubierto 22-09-2026 via API publica; slug=okta]</t>
         </is>
       </c>
     </row>
@@ -4496,17 +4508,17 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>https://ouraring.com/careers</t>
+          <t>https://job-boards.greenhouse.io/oura</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>[Salud] Anillo inteligente de salud y sueño</t>
+          <t>[Salud] Anillo inteligente de salud y sueño [ATS auto-descubierto 22-09-2026 via API publica; slug=oura]</t>
         </is>
       </c>
     </row>
@@ -4518,17 +4530,17 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>https://pachama.com/careers</t>
+          <t>https://job-boards.greenhouse.io/relae</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] Verificación de proyectos de carbono forestal</t>
+          <t>[Ecología] Verificación de proyectos de carbono forestal [ATS auto-descubierto 22-09-2026 via API publica; slug=relae]</t>
         </is>
       </c>
     </row>
@@ -4540,17 +4552,17 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4377843533/</t>
+          <t>https://job-boards.greenhouse.io/pandadoc</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Remoto · España / global · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remoto · España / global · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=pandadoc]</t>
         </is>
       </c>
     </row>
@@ -4606,17 +4618,17 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>https://www.patreon.com/careers</t>
+          <t>https://jobs.ashbyhq.com/patreon</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>[Impacto social] Economía de creadores</t>
+          <t>[Impacto social] Economía de creadores [ATS auto-descubierto 22-09-2026 via API publica; slug=patreon]</t>
         </is>
       </c>
     </row>
@@ -4650,17 +4662,17 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/search/?currentJobId=4408779313&amp;distance=25&amp;f_TPR=a1779180799-&amp;f_WT=1%2C3%2C2&amp;geoId=105646813&amp;keywords=User%20Experience%20Designer&amp;origin=JOB_ALERT_IN_APP_NOTIFICATION&amp;originToLandingJobPostings=4405549517%2C4415774953%2C4415943962%2C4416648658%2C4384089474%2C4407472278&amp;savedSearchId=5198310169</t>
+          <t>https://jobs.ashbyhq.com/pennylane</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Remote Europe · Remote · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remote Europe · Remote · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=pennylane]</t>
         </is>
       </c>
     </row>
@@ -4670,11 +4682,7 @@
           <t>Performanze</t>
         </is>
       </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.workflex.com/jobs/5091942-senior-ui-ux-designer</t>
-        </is>
-      </c>
+      <c r="B194" s="4" t="n"/>
       <c r="C194" s="4" t="inlineStr">
         <is>
           <t>no_se</t>
@@ -4682,7 +4690,7 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Madrid</t>
+          <t>Híbrido · Madrid [ATS detectado 22-09-2026 (teamtailor, slug=app) pero check_boards.py aun no lo soporta - revisar a mano] [22-09-2026: la URL guardada (careers.workflex.com) parece pertenecer a la empresa WorkFlex, no a Performanze -- posible error de datos en esta fila. Verificar y corregir la URL real de empleo de Performanze antes de fiarse de este board.] [22-09-2026 CORREGIDO: la URL que tenia guardada (careers.workflex.com) es en realidad de la empresa WorkFlex (confirmado: mismo dominio, mismo puesto "Senior UI/UX Designer" aparece bajo WorkFlex). Era un error de datos de origen, no una coincidencia real de Performanze. Se borra la URL hasta encontrar la web real de Performanze.]</t>
         </is>
       </c>
     </row>
@@ -4736,15 +4744,19 @@
           <t>Pillar</t>
         </is>
       </c>
-      <c r="B197" s="4" t="n"/>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/pillar</t>
+        </is>
+      </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Presencial · Barcelona · no tenías un enlace válido guardado para esta empresa en tu tracker</t>
+          <t>Presencial · Barcelona · no tenías un enlace válido guardado para esta empresa en tu tracker [ATS auto-descubierto 22-09-2026 via API publica; slug=pillar]</t>
         </is>
       </c>
     </row>
@@ -4756,17 +4768,17 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>https://plaid.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/plaid</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>[Fintech]</t>
+          <t>[Fintech] [ATS auto-descubierto 22-09-2026 via API publica; slug=plaid]</t>
         </is>
       </c>
     </row>
@@ -4778,17 +4790,17 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/collections/recommended/?currentJobId=4432376242&amp;discover=recommended&amp;discoveryOrigin=JOBS_HOME_JYMBII</t>
+          <t>https://jobs.ashbyhq.com/pleo</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Remote · Full-time · España · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remote · Full-time · España · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=pleo]</t>
         </is>
       </c>
     </row>
@@ -4800,17 +4812,17 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>https://preply.com/en/careers</t>
+          <t>https://jobs.ashbyhq.com/preply</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>[EdTech] Cofundadores ucranianos, oficina en Barcelona · También visto en tu tracker de aplicaciones: Hybrid · Full-time · Barcelona · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>[EdTech] Cofundadores ucranianos, oficina en Barcelona · También visto en tu tracker de aplicaciones: Hybrid · Full-time · Barcelona · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=preply] [22-09-2026: sin vacantes de diseno abiertas hoy (board vacio para Barcelona). No cuenta hoy, vigilar -- encaja mucho con el perfil (EdTech, Design Systems).]</t>
         </is>
       </c>
     </row>
@@ -4862,17 +4874,17 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>https://producthackers.teamtailor.com/jobs/6401103-product-designer-senior-ux-ui-espana</t>
+          <t>https://producthackers.teamtailor.com/jobs</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Remoto · España · Teamtailor</t>
+          <t>Remoto · España · Teamtailor [22-09-2026: ATS teamtailor confirmado (producthackers.teamtailor.com); hoy sin vacantes de diseno (solo Sales/Growth). No cuenta hoy.]</t>
         </is>
       </c>
     </row>
@@ -4884,17 +4896,17 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>https://app.joppy.me/explorer/offers/product-design/fe971bde-f2ee-4ce4-b5ac-879cfb038d33</t>
+          <t>https://job-boards.greenhouse.io/prophero</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Madrid · Visto vía Joppy</t>
+          <t>Híbrido · Madrid · Visto vía Joppy [ATS auto-descubierto 22-09-2026 via API publica; slug=prophero]</t>
         </is>
       </c>
     </row>
@@ -4911,12 +4923,12 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>icims</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>[Consultoría/Agencia]</t>
+          <t>[Consultoría/Agencia] [ATS detectado 22-09-2026 (icims, slug=referral-publicisgroupe) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -4972,17 +4984,17 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4390118070/?trk=eml-email_application_confirmation_with_nba_01-applied_jobs-0-jobcard_body_4390118070&amp;refId=zYu0NtMUTrmirK9rMLlxvg%3D%3D&amp;trackingId=%2Buqq%2FdjPRnKGm879QeSQCQ%3D%3D</t>
+          <t>https://jobs.ashbyhq.com/quantum</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Barcelona · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Híbrido · Barcelona · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=quantum]</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5052,7 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Remote-first · España · no tenías un enlace válido guardado para esta empresa en tu tracker · Agencia de UX/research española de referencia (Madrid) — buen fit directo</t>
+          <t>Remote-first · España · no tenías un enlace válido guardado para esta empresa en tu tracker · Agencia de UX/research española de referencia (Madrid) — buen fit directo [22-09-2026: oferta de UX/UI Product Designer ya cerrada ("This job is no longer available"). No cuenta hoy, vigilar.]</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5069,12 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Remoto · Barcerlona</t>
+          <t>Remoto · Barcerlona [ATS detectado 22-09-2026 (teamtailor, slug=www) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -5074,17 +5086,17 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>https://www.revolut.com/careers/</t>
+          <t>https://www.revolut.com/careers/team/product-design/</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>[Fintech] Presencia en Madrid · También visto en tu tracker de aplicaciones: Híbrido/Remoto · Madrid / Lisboa / Londres / Remote Internacional</t>
+          <t>[Fintech] Presencia en Madrid · También visto en tu tracker de aplicaciones: Híbrido/Remoto · Madrid / Lisboa / Londres / Remote Internacional [22-09-2026: "Product Designer (Platform)" confirmado en el board oficial con Madrid como oficina disponible (ademas de otro "Product Designer" con remoto en varios paises UE). No se pudo extraer la descripcion completa via navegador (carga dinamica); revisar a mano en revolut.com/careers/team/product-design/.]</t>
         </is>
       </c>
     </row>
@@ -5096,17 +5108,17 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>https://www.riotgames.com/en/work-with-us</t>
+          <t>https://job-boards.greenhouse.io/riotgames</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>[Gaming]</t>
+          <t>[Gaming] [ATS auto-descubierto 22-09-2026 via API publica; slug=riotgames]</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5130,7 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>https://careers.robinhood.com/</t>
+          <t>https://job-boards.greenhouse.io/robinhood</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -5128,7 +5140,7 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>[Fintech] Confirmado por Greenhouse como cliente</t>
+          <t>[Fintech] Confirmado por Greenhouse como cliente [ATS auto-descubierto 22-09-2026 via API publica; slug=robinhood]</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5201,12 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Remoto · Portugal / Germany / Netherlands / Spain · Workable</t>
+          <t>Remoto · Portugal / Germany / Netherlands / Spain · Workable [ATS detectado 22-09-2026 (workable, slug=samacoaching) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -5211,12 +5223,12 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>[Spain/Madrid] Sede en Madrid</t>
+          <t>[Spain/Madrid] Sede en Madrid [ATS detectado 22-09-2026 (workday, slug=santander) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -5488,17 +5500,17 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>https://www.socialpoint.es/careers</t>
+          <t>https://job-boards.greenhouse.io/spcareers</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>[Gaming] Estudio en Barcelona, parte de Take-Two</t>
+          <t>[Gaming] Estudio en Barcelona, parte de Take-Two [22-09-2026: ATS auto-descubierto (greenhouse) via discover_v2 sistematizado, sin oferta de diseno hoy salvo excepcion anotada aparte.]</t>
         </is>
       </c>
     </row>
@@ -5515,12 +5527,12 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>verificar</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Remote-first · Germany</t>
+          <t>Remote-first · Germany [22-09-2026: socialhub.io/karriere — Personio detectado, anadir soporte XML/API mas adelante]</t>
         </is>
       </c>
     </row>
@@ -5576,17 +5588,17 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/search-results/?currentJobId=4436243892&amp;eBP=NOT_ELIGIBLE_FOR_CHARGING&amp;refId=gqWpkfQJH%2F17koWETP4aAA%3D%3D&amp;trackingId=dRZMUHAOkNaNZ3FktbYfpA%3D%3D&amp;keywords=product%20Designer%20posted%20in%20the%20past%202%20days&amp;origin=SEMANTIC_SEARCH_LANDING_PAGE</t>
+          <t>https://jobs.lever.co/spinai</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Hybrid · Full-time · Málaga (España) · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Hybrid · Full-time · Málaga (España) · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=spinai]</t>
         </is>
       </c>
     </row>
@@ -5598,17 +5610,17 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>https://www.lifeatspotify.com/</t>
+          <t>https://jobs.lever.co/spotify</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>[Música/Streaming]</t>
+          <t>[Música/Streaming] [ATS auto-descubierto 22-09-2026 via API publica; slug=spotify]</t>
         </is>
       </c>
     </row>
@@ -5620,17 +5632,17 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>https://careers.stravito.com/jobs/7342996-product-designer</t>
+          <t>https://careers.stravito.com/jobs</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Remote-first · Spain/Europe</t>
+          <t>Remote-first · Spain/Europe [22-09-2026: ATS auto-descubierto (teamtailor) via discover_v2 sistematizado, sin oferta de diseno hoy salvo excepcion anotada aparte.]</t>
         </is>
       </c>
     </row>
@@ -5642,17 +5654,17 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs</t>
+          <t>https://job-boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>[Fintech] · También visto en tu tracker de aplicaciones: Remote · España · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>[Fintech] · También visto en tu tracker de aplicaciones: Remote · España · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=stripe]</t>
         </is>
       </c>
     </row>
@@ -5686,17 +5698,17 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>https://sme.careers/dashboard</t>
+          <t>https://jobs.lever.co/superannotate</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Remote · Global · Tu comentario original: mala experiencia con entrevista con IA en el proceso</t>
+          <t>Remote · Global · Tu comentario original: mala experiencia con entrevista con IA en el proceso [ATS auto-descubierto 22-09-2026 via API publica; slug=superannotate]</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5720,7 @@
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/superbet/jobs/4776704101</t>
+          <t>https://job-boards.eu.greenhouse.io/super/jobs/4940488101</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
@@ -5718,7 +5730,7 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Híbrido /  / Remoto · España · Super Technologies aparece junto a Superbet en tu tracker, probablemente su unidad tech</t>
+          <t>Slug de Greenhouse cambiado de 'superbet' a 'super' (Super Technologies) el ~sept-2026; URLs viejas /superbet/jobs/... dan 404. Board activo: job-boards.eu.greenhouse.io/super. Hibrido/Remoto Espana. En este entorno la API boards-api.eu.greenhouse.io no resuelve (DNS).</t>
         </is>
       </c>
     </row>
@@ -5730,17 +5742,17 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>https://supercell.com/en/careers/</t>
+          <t>https://jobs.ashbyhq.com/supercell</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>[Gaming]</t>
+          <t>[Gaming] [ATS auto-descubierto 22-09-2026 via API publica; slug=supercell]</t>
         </is>
       </c>
     </row>
@@ -5774,17 +5786,17 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4405549517/</t>
+          <t>https://jobs.ashbyhq.com/terra</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Remoto · Bilbao / remoto · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remoto · Bilbao / remoto · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=terra]</t>
         </is>
       </c>
     </row>
@@ -5796,17 +5808,17 @@
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/theam/8ab3b02b-101c-43e7-a5d0-a07fdba62510?utm_source=KQny0YMw1V</t>
+          <t>https://app.dover.com/The%20Agile%20Monkeys/careers/41d64f40-6cf2-4fc9-ae12-67a460623bc3</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>España / Las Palmas / Madrid · Remote-first</t>
+          <t>Espana / Las Palmas / Madrid - Remote-first. 31-08-2026: abandonaron Ashby (slug theam devuelve 404 desde 15-07); ahora usan Dover (SPA no monitorizable por check_boards). Marcado como otro para que el script no gaste un timeout en el. Revisar el board de Dover a mano.</t>
         </is>
       </c>
     </row>
@@ -5862,17 +5874,17 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>https://careers.thinkproject.com/Senior-UXUI-Designer-fmd-eng-j1521.html</t>
+          <t>https://careers.thinkproject.com/</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Hybrid · Madrid</t>
+          <t>Hybrid · Madrid [22-09-2026: Senior UX/UI Designer confirmado abierto, Madrid hibrido, B2B SaaS, WCAG 2.2 AA y Design Systems explicitos -- gran encaje. Aplicar ya.]</t>
         </is>
       </c>
     </row>
@@ -5884,17 +5896,17 @@
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers</t>
+          <t>https://job-boards.greenhouse.io/thoughtworks</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>[Consultoría/Agencia]</t>
+          <t>[Consultoría/Agencia] [ATS auto-descubierto 22-09-2026 via API publica; slug=thoughtworks]</t>
         </is>
       </c>
     </row>
@@ -5906,17 +5918,17 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>https://tonyschocolonely.com/us/en/careers</t>
+          <t>https://jobs.tonyschocolonely.com</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>recruitee</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>[Ecología/Impacto social] Chocolate contra la esclavitud infantil, B-Corp</t>
+          <t>[Ecología/Impacto social] Chocolate contra la esclavitud infantil, B-Corp [22-09-2026: ATS auto-descubierto (recruitee) via discover_v2 sistematizado, sin oferta de diseno hoy salvo excepcion anotada aparte.]</t>
         </is>
       </c>
     </row>
@@ -5928,17 +5940,17 @@
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>https://careers.toogoodtogo.com/</t>
+          <t>https://jobs.ashbyhq.com/toogoodtogo</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] App contra el desperdicio de comida, muy presente en España</t>
+          <t>[Ecología] App contra el desperdicio de comida, muy presente en España [ATS auto-descubierto 22-09-2026 via API publica; slug=toogoodtogo]</t>
         </is>
       </c>
     </row>
@@ -5994,17 +6006,17 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/collections/recommended/?currentJobId=4404572934&amp;discover=recommended&amp;discoveryOrigin=JOBS_HOME_JYMBII</t>
+          <t>https://job-boards.greenhouse.io/tribal</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Híbrido (1 día oficina) · Madrid · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Híbrido (1 día oficina) · Madrid · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=tribal]</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6033,12 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>verificar</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Híbrido (3 días oficina) · Madrid (Arturo Soria) · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Híbrido (3 días oficina) · Madrid (Arturo Soria) · enlace guardado es de LinkedIn, no la web oficial [22-09-2026: tribbuapp.com — Personio detectado]</t>
         </is>
       </c>
     </row>
@@ -6082,17 +6094,17 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>https://www.twilio.com/en-us/company/jobs</t>
+          <t>https://job-boards.greenhouse.io/twilio</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS auto-descubierto 22-09-2026 via API publica; slug=twilio]</t>
         </is>
       </c>
     </row>
@@ -6104,17 +6116,17 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>https://www.typeform.com/careers/</t>
+          <t>https://job-boards.greenhouse.io/typeform</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B] Con sede en Barcelona · También visto en tu tracker de aplicaciones: Remote · Spain/Europe</t>
+          <t>[SaaS B2B] Con sede en Barcelona · También visto en tu tracker de aplicaciones: Remote · Spain/Europe [ATS auto-descubierto 22-09-2026 via API publica; slug=typeform]</t>
         </is>
       </c>
     </row>
@@ -6148,17 +6160,17 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>https://www.udemy.com/careers/</t>
+          <t>https://job-boards.greenhouse.io/udemy</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>[EdTech]</t>
+          <t>[EdTech] [ATS auto-descubierto 22-09-2026 via API publica; slug=udemy]</t>
         </is>
       </c>
     </row>
@@ -6170,17 +6182,17 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/collections/recommended/?currentJobId=4375521994&amp;discover=recommended&amp;discoveryOrigin=JOBS_HOME_JYMBII</t>
+          <t>https://job-boards.greenhouse.io/veriff</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>Spain (Remote) · Remote · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Spain (Remote) · Remote · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=veriff]</t>
         </is>
       </c>
     </row>
@@ -6214,17 +6226,17 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>https://about.wallapop.com/en/careers/</t>
+          <t>https://job-boards.greenhouse.io/wallapop</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>[Spain/Madrid] Sede en Barcelona</t>
+          <t>[Spain/Madrid] Sede en Barcelona [ATS auto-descubierto 22-09-2026 via API publica; slug=wallapop]</t>
         </is>
       </c>
     </row>
@@ -6280,17 +6292,17 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>https://watershed.com/careers</t>
+          <t>https://job-boards.greenhouse.io/watershed</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>[Ecología] Software de gestión de huella de carbono para empresas</t>
+          <t>[Ecología] Software de gestión de huella de carbono para empresas [ATS auto-descubierto 22-09-2026 via API publica; slug=watershed]</t>
         </is>
       </c>
     </row>
@@ -6346,17 +6358,17 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>https://webflow.com/careers</t>
+          <t>https://job-boards.greenhouse.io/webflow</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>[Design/producto]</t>
+          <t>[Design/producto] [ATS auto-descubierto 22-09-2026 via API publica; slug=webflow]</t>
         </is>
       </c>
     </row>
@@ -6368,17 +6380,17 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>https://www.whoop.com/careers/</t>
+          <t>https://jobs.lever.co/whoop</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>[Salud] Wearable de rendimiento y recuperación</t>
+          <t>[Salud] Wearable de rendimiento y recuperación [ATS auto-descubierto 22-09-2026 via API publica; slug=whoop]</t>
         </is>
       </c>
     </row>
@@ -6390,17 +6402,17 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>https://wikimediafoundation.org/about/jobs/</t>
+          <t>https://job-boards.greenhouse.io/wikimedia</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>[Impacto social] Organización sin ánimo de lucro tras Wikipedia</t>
+          <t>[Impacto social] Organización sin ánimo de lucro tras Wikipedia [ATS auto-descubierto 22-09-2026 via API publica; slug=wikimedia]</t>
         </is>
       </c>
     </row>
@@ -6412,17 +6424,17 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>https://wise.jobs/</t>
+          <t>https://job-boards.greenhouse.io/wise</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>[Fintech]</t>
+          <t>[Fintech] [ATS auto-descubierto 22-09-2026 via API publica; slug=wise]</t>
         </is>
       </c>
     </row>
@@ -6434,17 +6446,17 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4400317259/</t>
+          <t>https://job-boards.greenhouse.io/wizeline</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Híbrido · Barcelona · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Híbrido · Barcelona · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=wizeline]</t>
         </is>
       </c>
     </row>
@@ -6456,17 +6468,17 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4423641390/?trk=eml-email_jobs_application_rejected_01-applied_jobs-0-applied_job</t>
+          <t>https://careers.workflex.com/jobs</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>teamtailor</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Remoto 100% · Europa (remote) · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Remoto 100% · Europa (remote) · enlace guardado es de LinkedIn, no la web oficial [22-09-2026: ATS auto-descubierto (teamtailor) via discover_v2 sistematizado, sin oferta de diseno hoy salvo excepcion anotada aparte.]</t>
         </is>
       </c>
     </row>
@@ -6500,17 +6512,17 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/search-results/?currentJobId=4413029816&amp;eBP=NOT_ELIGIBLE_FOR_CHARGING&amp;refId=FEYWEM%2BMCh2q%2FOXsqg9Hsg%3D%3D&amp;trackingId=OIf4gBcFJYc4qL%2BmHXiAoQ%3D%3D&amp;keywords=product%20designer&amp;origin=JOB_SEARCH_PAGE_JOB_FILTER&amp;referralSearchId=3UXZO4Zvpbd%2BLxvWL%2Fmk1Q%3D%3D&amp;start=50&amp;f_TPR=r604800</t>
+          <t>https://jobs.ashbyhq.com/xe</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Híbrido (2 días WFH) · Alcobendas, Madrid · enlace guardado es de LinkedIn, no la web oficial</t>
+          <t>Híbrido (2 días WFH) · Alcobendas, Madrid · enlace guardado es de LinkedIn, no la web oficial [ATS auto-descubierto 22-09-2026 via API publica; slug=xe]</t>
         </is>
       </c>
     </row>
@@ -6520,15 +6532,19 @@
           <t>Xsolla</t>
         </is>
       </c>
-      <c r="B279" s="4" t="n"/>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/xsolla</t>
+        </is>
+      </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>No especificado (probablemente remote/híbrido internacional) · Global / gaming</t>
+          <t>No especificado (probablemente remote/híbrido internacional) · Global / gaming [ATS auto-descubierto 22-09-2026 via API publica; slug=xsolla]</t>
         </is>
       </c>
     </row>
@@ -6540,17 +6556,17 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>https://www.yazio.com/en/open-positions?utm_source=j99GyPOY10&amp;ashby_jid=4cf41fd3-d172-4d1b-a242-b4024374d8f3</t>
+          <t>https://jobs.ashbyhq.com/yazio</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>no_se</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Remote · Spain / Germany / Portugal / UK</t>
+          <t>Remote · Spain / Germany / Portugal / UK [ATS auto-descubierto 22-09-2026 via API publica; slug=yazio]</t>
         </is>
       </c>
     </row>
@@ -6624,17 +6640,17 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>https://zapier.com/jobs</t>
+          <t>https://jobs.ashbyhq.com/zapier</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>[Remote-first] Cultura 100% remota</t>
+          <t>[Remote-first] Cultura 100% remota [ATS auto-descubierto 22-09-2026 via API publica; slug=zapier]</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6667,12 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>verificar</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>[SaaS B2B]</t>
+          <t>[SaaS B2B] [ATS detectado 22-09-2026 (workday, slug=zendesk) pero check_boards.py aun no lo soporta - revisar a mano]</t>
         </is>
       </c>
     </row>
@@ -6701,6 +6717,446 @@
       <c r="D287" s="4" t="inlineStr">
         <is>
           <t>[Ecología] Líder mundial en energía eólica marina</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Oneleet</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/oneleet</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>B2B security/compliance SaaS (Series A). Encontrada 20-07-2026 con Senior Product Designer abierto, remoto US/EU. Encaja bien con perfil B2B SaaS/enterprise/accesibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Mediagenix</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/mediagenix</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>B2B SaaS para medios (media management). Sin vacantes de diseño el 20-07-2026, pero ha publicado Product/Senior Product Designer antes -- vigilar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Hospitable</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://apply.workable.com/hospitable</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>workable</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>SaaS gestion de alquileres vacacionales (Airbnb hosts), remote-first. ATS Workable (no auto-consultable por check_boards.py). Encontrada 20-07-2026 con Staff UI/UX Product Designer abierto, elegible desde Espana. [ATS detectado 22-09-2026 (workable, slug=hospitable) pero check_boards.py aun no lo soporta - revisar a mano]</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>BVNK</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/bvnk</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Fintech B2B: infraestructura de pagos con stablecoins. Encontrada 22-07-2026 con Lead Product Designer - Design System y Principal Product Designer - Core Platform abiertos, Espana incluida entre ubicaciones. Encaja con perfil B2B/plataformas complejas pero ambos roles piden nivel Lead/Principal muy por encima de la experiencia documentada en resume.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Aircall</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/aircall</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>SaaS B2B comunicaciones/AI (unicornio, HQ Paris, oficina Madrid). Encontrada 31-08-2026 con Senior Product Designer (Madrid, hibrido) abierta. Encaja con perfil B2B SaaS/AI/flujos complejos; rol de founding/solo designer con triple mandato -&gt; Merece un vistazo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Launchmetrics</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://careers.launchmetrics.com/jobs</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>teamtailor</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>SaaS B2B Brand Performance Cloud para moda/lujo/belleza (oficinas Paris/Milan/Girona/Madrid). Ritmo de contratacion de diseno (Associate/Senior/Lead PD vistos). ATS Teamtailor, no monitorizable por check_boards. Encontrada 31-08-2026 con Associate Product Designer abierta (nivel entry, por debajo del perfil). [ATS detectado 22-09-2026 (teamtailor, slug=app) pero check_boards.py aun no lo soporta - revisar a mano]</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Remote.com</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/remotecom/jobs/7762220003</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>B2B SaaS empleo/nomina global. Fully remote EMEA. Design system 'Norma', accesibilidad, research. Anadida 06-09-2026 (revision diaria).</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>EverAI</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/everai/3068ad20-23ae-49c0-a611-a38c9809b98c</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>AI companionship (producto consumer, contenido NSFW). Remoto Europa. Contrata varios Senior Product Designer por pais. Anadida 06-09-2026 (revision diaria).</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>lemlist</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/lemlist</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>[B2B SaaS / Sales tech AI] Bootstrapped, $50M+ ARR, 40k+ equipos. Contrata Product Design. Anadida 09-09-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Hostaway</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://careers.hostaway.com/</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>[B2B SaaS / PropTech PMS] Unicornio short-term rental, 100% remoto EMEA. Varias vacantes de diseno. check_boards NO soporta Recruitee - revisar a mano. Anadida 09-09-2026. [ATS detectado 22-09-2026 (recruitee, slug=careers-analytics) pero check_boards.py aun no lo soporta - revisar a mano]</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Miaplaza</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://miaplaza.recruitee.com/</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>[EdTech B2C] Plataformas homeschool (Miacademy/MiaPrep), 150k+ alumnos, equipo de diseno pequeno y senior, accesibilidad para publico neurodivergente. check_boards NO soporta Recruitee. Anadida 09-09-2026. [ATS detectado 22-09-2026 (recruitee, slug=miaplaza) pero check_boards.py aun no lo soporta - revisar a mano]</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Finom</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/finom</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>[Fintech B2B] Plataforma financiera all-in-one para autonomos/pymes en la UE (banca+contabilidad+facturacion), sede Amsterdam, Serie C (~346M$ levantados). Contrata varios Senior Product Designer (Credit &amp; Cards) en paralelo, remoto UE / hibrido, oferta con presencia en Espana. ATS es Lever EU (api.eu.lever.co) - check_boards.py solo consulta api.lever.co (no EU), por eso NO se puede automatizar sin tocar el script; revisar a mano. Anadida 12-09-2026. [ATS auto-descubierto 22-09-2026 via API publica; slug=finom]</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Insense</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://insense.na.teamtailor.com/jobs</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>teamtailor</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>[SaaS B2B - marketplace de creadores/UGC para marcas eCom] Remote-first, 60+ personas. Vacante puntual: Senior Product Designer (contrato 6 meses, cobertura de sabatico), incluye opcion Valencia. check_boards.py NO soporta Teamtailor - revisar a mano. Anadida 12-09-2026. [ATS detectado 22-09-2026 (teamtailor, slug=na) pero check_boards.py aun no lo soporta - revisar a mano]</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>TryHackMe</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://careers.tryhackme.com/jobs</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>teamtailor</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>[EdTech/B2B - plataforma de formacion en ciberseguridad gamificada, 8M+ usuarios, 170+ empleados] Encontrada 15-09-2026 con 3 vacantes de diseno abiertas en paralelo: Product Designer (B2B), Product Designer (B2C), Growth Product Designer - todas 100% remoto, sin patrocinio de visado. check_boards.py NO soporta Teamtailor - revisar a mano (mismo caso que Insense). [ATS detectado 22-09-2026 (teamtailor, slug=www) pero check_boards.py aun no lo soporta - revisar a mano]</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>[Enterprise software B2B - process mining] Encontrada 15-09-2026. Unico puesto de diseno activo hoy es Senior Design Engineer, Design System (Madrid/Munich) - requiere construir componentes en produccion en Angular/TypeScript, no encaja con el perfil (no hay skills de codigo en resume.md), por eso NO se puntuo como oferta. Se anade igualmente porque la empresa tiene ritmo de contratacion de diseno de producto (historial de vacantes Staff Product Designer y Staff Accessibility Designer - Design System). ATS Greenhouse estandar (no EU) - SI deberia poder monitorizarse automaticamente con check_boards.py desde la proxima ejecucion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>WunderGraph</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/wundergraph</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>[Developer tools B2B - plataforma de GraphQL Federation / API management, Series A (7.5M USD, marzo 2025), backed por eBay/Karma Ventures/Aspenwood]. Vacante activa 16-09-2026: Senior Product Designer EMEA, 100% remoto (prioriza EMEA/horario CET), rol generalista que cubre product design + UX research + design system + marketing/brand. ATS Ashby (slug wundergraph), deberia ser detectable automaticamente por check_boards.py. Anadida 16-09-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>RemoFirst</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/remofirst/63afeacf-d50c-4cfd-a394-446728a02d52</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>B2B SaaS global HR/EOR platform (nomina, compliance multipais). Encontrada 18-09-2026 con Senior Product Designer 100% remoto (Espana entre paises elegibles). Encaja con perfil B2B SaaS/plataformas complejas/accesibilidad; pide minimo 5 anos (resume 4+) -&gt; Merece un vistazo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Resend</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/resend</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>[Developer tools - plataforma de envio de email, equipo 50 personas, a16z/YC] Encontrada 21-09-2026 con Product Designer (Europe) 100% remoto, sin anos concretos exigidos. ATS Ashby (slug resend), detectable por check_boards.py. Aplicar ya el 21-09-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/n8n</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>[AI workflow orchestration / developer tools B2B, 260+ personas, valoracion 5.2bn USD] Encontrada 21-09-2026 con Senior/Staff Product Designer True Remote (Spain elegible), pide 5+ anos. Ademas hay Head of Product Design y Design Talent Pool abiertos: ritmo de contratacion de diseno alto. ATS Ashby (slug n8n).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Secfix</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/secfix</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>[SaaS B2B compliance (ISO 27001/SOC 2), Series A 12M EUR] Encontrada 21-09-2026 con Senior Product Designer remoto EMEA; pide 8+ anos (Merece un vistazo). Contratando tercer disenador, vigilar por si abren un puesto mas junior. ATS Ashby (slug secfix).</t>
         </is>
       </c>
     </row>
